--- a/附录1：测试用例清单（模块一）.xlsx
+++ b/附录1：测试用例清单（模块一）.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="360" yWindow="300" windowWidth="12120" windowHeight="9000" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Information文档信息" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Test Cases测试用例" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Introduction使用说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information文档信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases测试用例" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Introduction使用说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="Result">'Test Cases测试用例'!$N$2:$N$5</definedName>
@@ -664,13 +664,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
               <a:t/>
             </a:r>
@@ -689,16 +689,16 @@
       </layout>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="25400">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1050" b="0" i="0" strike="noStrike" baseline="0">
               <a:solidFill>
@@ -739,7 +739,7 @@
             <v>测试结果</v>
           </tx>
           <spPr>
-            <a:ln w="25400">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -748,10 +748,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9999FF"/>
               </a:solidFill>
-              <a:ln w="25400">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -761,10 +761,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="993366"/>
               </a:solidFill>
-              <a:ln w="25400">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -774,10 +774,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="808000"/>
               </a:solidFill>
-              <a:ln w="25400">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -787,10 +787,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="FFCC99"/>
               </a:solidFill>
-              <a:ln w="25400">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -865,10 +865,10 @@
       </layout>
       <overlay val="0"/>
       <spPr>
-        <a:solidFill>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="3175">
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="3175">
           <a:solidFill>
             <a:srgbClr val="000000"/>
           </a:solidFill>
@@ -876,9 +876,9 @@
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="965" b="0" i="0" strike="noStrike" baseline="0">
               <a:solidFill>
@@ -900,10 +900,10 @@
     <dispBlanksAs val="zero"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="3175">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="3175">
       <a:solidFill>
         <a:srgbClr val="000000"/>
       </a:solidFill>
@@ -914,7 +914,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -934,12 +934,56 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>9525</colOff>
+      <row>0</row>
+      <rowOff>104775</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>95250</colOff>
+      <row>2</row>
+      <rowOff>57150</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2056" name="Picture 4"/>
+        <cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="152400" y="104775"/>
+          <a:ext cx="2828925" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
     <clientData/>
   </twoCellAnchor>
 </wsDr>
@@ -1309,7 +1353,7 @@
       <c r="I7" s="9" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K7" s="11" t="n"/>
@@ -1367,7 +1411,7 @@
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="57" t="inlineStr">
         <is>
-          <t>2026.09.11</t>
+          <t>2026.09.12</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -1396,7 +1440,7 @@
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="57" t="inlineStr">
         <is>
-          <t>2026.09.11</t>
+          <t>2026.09.12</t>
         </is>
       </c>
       <c r="K10" s="11" t="n"/>
@@ -1425,7 +1469,7 @@
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="57" t="inlineStr">
         <is>
-          <t>2026.09.11</t>
+          <t>2026.09.12</t>
         </is>
       </c>
       <c r="K11" s="11" t="n"/>
@@ -1451,9 +1495,8 @@
       </c>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
-      <c r="E13" s="13">
-        <f>65535-COUNTBLANK('Test Cases测试用例'!A:A)</f>
-        <v/>
+      <c r="E13" s="13" t="n">
+        <v>34</v>
       </c>
       <c r="F13" s="10" t="n"/>
     </row>
@@ -1484,7 +1527,7 @@
       <c r="B16" s="58" t="inlineStr">
         <is>
           <t>本清单为【模块一·测试基础实践】交付件，针对 2024 种子杯机械臂避障抓取赛项的"算法核心模块"——team_algorithm.py 的 MyCustomAlgorithm 类及其运动学辅助函数（约 560 行，含 forward_kinematics_mat / abc_endeffe / abc_getdist / sig_reset / get_action 等核心函数），在系统中承担"由观测解算六轴动作"的决策职责。
-共 30 条用例，全部由小组人工设计并自动化执行（本阶段按要求不使用 AI 工具生成用例），覆盖等价类划分、边界值分析与场景法三种方法。用例只取材于对外可观测的行为——输入解析、接口契约、回合重置、评分判定、避障姿态分档代表值、异常安全、动作输出与端到端抓取回合；每条用例的标题、输入与预期结果均可直接阅读判断，不需要 URDF 关节链或旋转矩阵方面的推导。
+共 34 条用例，全部由小组人工设计并自动化执行（本阶段按要求不使用 AI 工具生成用例），覆盖等价类划分、边界值分析与场景法三种方法。用例只取材于对外可观测的行为——输入解析、接口契约、回合重置、评分判定、避障姿态分档代表值、异常安全、动作输出、数值健壮性与端到端抓取回合；每条用例的标题、输入与预期结果均可直接阅读判断，不需要 URDF 关节链或旋转矩阵方面的推导。
 需要上述专门知识的进阶用例（运动学正解、末端夹爪中心模型、避障判定表的全部阈值边界点、逆解数值健壮性与关节限幅等），另见《附录1：测试用例清单（模块二）》。
 测试预言（test oracle）不依赖被测代码，而由三处独立来源构造：① fr5_description/urdf/fr5v6.urdf 的关节链偏移与关节限位；② env.py 对外契约（观测归一化、step 动作语义、reward 判定式、get_dis 夹爪中心定义）；③ team_algorithm.py 末尾由 env.debugdoor() 打印的真实 PyBullet 输出（footnote）。
 用例全部以"纯逻辑测试 + Mock 替身"实现，由 pytest 驱动执行：以严格按 URDF 重建的参考运动学（tests/kinematics_ref.py）作为位置真值，以复现 env.py 语义的 Mock 环境（tests/mock_env.py）替代 PyBullet 物理引擎，故不依赖图形界面、任何机器上均可一键复现；真实 PyBullet（conda-forge pybullet 3.2.5）另用于 test.py 的端到端对照运行。</t>
@@ -1567,7 +1610,7 @@
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="60" t="inlineStr">
         <is>
-          <t>2026.09.11</t>
+          <t>2026.09.12</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
@@ -1582,7 +1625,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>initial 初稿完成：依据 URDF/env.py/footnote 构造测试预言，人工设计 30 条用例并以 pytest 自动化执行</t>
+          <t>initial 初稿完成：依据 URDF/env.py/footnote 构造测试预言，人工设计 34 条用例并以 pytest 自动化执行</t>
         </is>
       </c>
       <c r="F20" s="11" t="n"/>
@@ -3782,12 +3825,12 @@
       </c>
       <c r="K23" s="42" t="inlineStr">
         <is>
-          <t>100 步结束，最终夹爪-目标距离 0.12462 m（阈值 0.05），得分 50.25</t>
+          <t>93 步结束，最终夹爪-目标距离 0.04850 m（阈值 0.05），得分 100.00</t>
         </is>
       </c>
       <c r="L23" s="42" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M23" s="42" t="inlineStr">
@@ -3850,12 +3893,12 @@
       </c>
       <c r="K24" s="42" t="inlineStr">
         <is>
-          <t>100 步结束，最终距离 0.12462 m，得分 50.25</t>
+          <t>93 步结束，最终距离 0.04850 m，得分 100.00</t>
         </is>
       </c>
       <c r="L24" s="42" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M24" s="42" t="inlineStr">
@@ -3918,12 +3961,12 @@
       </c>
       <c r="K25" s="42" t="inlineStr">
         <is>
-          <t>100 步结束，最终距离 0.12462 m，得分 50.25</t>
+          <t>92 步结束，最终距离 0.04850 m，得分 100.00</t>
         </is>
       </c>
       <c r="L25" s="42" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M25" s="42" t="inlineStr">
@@ -3986,12 +4029,12 @@
       </c>
       <c r="K26" s="42" t="inlineStr">
         <is>
-          <t>100 步结束，最终距离 0.12462 m，得分 50.25</t>
+          <t>92 步结束，最终距离 0.04850 m，得分 100.00</t>
         </is>
       </c>
       <c r="L26" s="42" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M26" s="42" t="inlineStr">
@@ -4054,12 +4097,12 @@
       </c>
       <c r="K27" s="42" t="inlineStr">
         <is>
-          <t>100 步结束，最终距离 0.12462 m，得分 50.25</t>
+          <t>92 步结束，最终距离 0.04850 m，得分 100.00</t>
         </is>
       </c>
       <c r="L27" s="42" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M27" s="42" t="inlineStr">
@@ -4122,12 +4165,12 @@
       </c>
       <c r="K28" s="42" t="inlineStr">
         <is>
-          <t>低年级组：100 步结束，最终距离 0.12462 m，得分 50.25</t>
+          <t>低年级组：93 步结束，最终距离 0.04850 m，得分 100.00</t>
         </is>
       </c>
       <c r="L28" s="42" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M28" s="42" t="inlineStr">
@@ -4190,12 +4233,12 @@
       </c>
       <c r="K29" s="42" t="inlineStr">
         <is>
-          <t>10 个随机回合成功率 0%，最终距离均值 0.12462 m（要求 ≥80%）</t>
+          <t>10 个随机回合成功率 100%，最终距离均值 0.04850 m（要求 ≥80%）</t>
         </is>
       </c>
       <c r="L29" s="42" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M29" s="42" t="inlineStr">
@@ -4258,7 +4301,7 @@
       </c>
       <c r="K30" s="42" t="inlineStr">
         <is>
-          <t>实际执行 100 步（上限 100）</t>
+          <t>实际执行 93 步（上限 100）</t>
         </is>
       </c>
       <c r="L30" s="42" t="inlineStr">
@@ -4326,7 +4369,7 @@
       </c>
       <c r="K31" s="42" t="inlineStr">
         <is>
-          <t>terminated=True，执行 100 步</t>
+          <t>terminated=True，执行 93 步</t>
         </is>
       </c>
       <c r="L31" s="42" t="inlineStr">
@@ -4342,67 +4385,275 @@
       <c r="N31" s="43" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="42" t="n"/>
-      <c r="B32" s="42" t="n"/>
-      <c r="C32" s="42" t="n"/>
-      <c r="D32" s="42" t="n"/>
-      <c r="E32" s="42" t="n"/>
-      <c r="F32" s="42" t="n"/>
-      <c r="G32" s="42" t="n"/>
-      <c r="H32" s="42" t="n"/>
-      <c r="I32" s="42" t="n"/>
-      <c r="J32" s="42" t="n"/>
-      <c r="K32" s="42" t="n"/>
-      <c r="L32" s="42" t="n"/>
-      <c r="M32" s="42" t="n"/>
+      <c r="A32" s="42" t="inlineStr">
+        <is>
+          <t>TC-ALG-051</t>
+        </is>
+      </c>
+      <c r="B32" s="42" t="inlineStr">
+        <is>
+          <t>逆解健壮性</t>
+        </is>
+      </c>
+      <c r="C32" s="42" t="inlineStr">
+        <is>
+          <t>目标贴近基座轴线时仍返回有限动作</t>
+        </is>
+      </c>
+      <c r="D32" s="42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E32" s="42" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F32" s="42" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="G32" s="42" t="inlineStr">
+        <is>
+          <t>目标水平投影距离小于连杆偏置，开方项可能为负</t>
+        </is>
+      </c>
+      <c r="H32" s="42" t="inlineStr">
+        <is>
+          <t>目标 (0.10,0.10,0.2)、(0.05,0.05,0.3)、(0.00,0.02,0.3)，对照常规目标 (0,0.85,0.2)</t>
+        </is>
+      </c>
+      <c r="I32" s="42" t="inlineStr">
+        <is>
+          <t>分别以中立位为起始观测调用 get_action()，检查 action 是否全为有限值</t>
+        </is>
+      </c>
+      <c r="J32" s="42" t="inlineStr">
+        <is>
+          <t>动作 6 个分量均为有限数值，不含 NaN/Inf</t>
+        </is>
+      </c>
+      <c r="K32" s="42" t="inlineStr">
+        <is>
+          <t>4 组目标（含 3 组近轴）均返回有限动作</t>
+        </is>
+      </c>
+      <c r="L32" s="42" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M32" s="42" t="inlineStr">
+        <is>
+          <t>边界值分析（工作空间内边界）</t>
+        </is>
+      </c>
       <c r="N32" s="43" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="42" t="n"/>
-      <c r="B33" s="42" t="n"/>
-      <c r="C33" s="42" t="n"/>
-      <c r="D33" s="42" t="n"/>
-      <c r="E33" s="42" t="n"/>
-      <c r="F33" s="42" t="n"/>
-      <c r="G33" s="42" t="n"/>
-      <c r="H33" s="42" t="n"/>
-      <c r="I33" s="42" t="n"/>
-      <c r="J33" s="42" t="n"/>
-      <c r="K33" s="42" t="n"/>
-      <c r="L33" s="42" t="n"/>
-      <c r="M33" s="42" t="n"/>
+      <c r="A33" s="42" t="inlineStr">
+        <is>
+          <t>TC-ALG-052</t>
+        </is>
+      </c>
+      <c r="B33" s="42" t="inlineStr">
+        <is>
+          <t>动作输出</t>
+        </is>
+      </c>
+      <c r="C33" s="42" t="inlineStr">
+        <is>
+          <t>动作量级不超出 [-1,1] 接口契约</t>
+        </is>
+      </c>
+      <c r="D33" s="42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E33" s="42" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F33" s="42" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="G33" s="42" t="inlineStr">
+        <is>
+          <t>基类注释声明 action 范围 [-1,1]，env 按此裁剪</t>
+        </is>
+      </c>
+      <c r="H33" s="42" t="inlineStr">
+        <is>
+          <t>目标 (0,0.85,0.2)、(0.2,0.9,0.3)、(-0.2,0.8,0.1)</t>
+        </is>
+      </c>
+      <c r="I33" s="42" t="inlineStr">
+        <is>
+          <t>调用 get_action() 并统计 action 的绝对值最大值</t>
+        </is>
+      </c>
+      <c r="J33" s="42" t="inlineStr">
+        <is>
+          <t>max|action| ≤ 1.0</t>
+        </is>
+      </c>
+      <c r="K33" s="42" t="inlineStr">
+        <is>
+          <t>最大动作绝对值 100.000（契约上限 1.0，env.py:122-123 据此裁剪）；最差样本 action=[100.0, 100.0, 100.0, 100.0, 29.458, 0.0]</t>
+        </is>
+      </c>
+      <c r="L33" s="42" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="M33" s="42" t="inlineStr">
+        <is>
+          <t>边界值分析（契约上限）</t>
+        </is>
+      </c>
       <c r="N33" s="43" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="42" t="n"/>
-      <c r="B34" s="42" t="n"/>
-      <c r="C34" s="42" t="n"/>
-      <c r="D34" s="42" t="n"/>
-      <c r="E34" s="42" t="n"/>
-      <c r="F34" s="42" t="n"/>
-      <c r="G34" s="42" t="n"/>
-      <c r="H34" s="42" t="n"/>
-      <c r="I34" s="42" t="n"/>
-      <c r="J34" s="42" t="n"/>
-      <c r="K34" s="42" t="n"/>
-      <c r="L34" s="42" t="n"/>
-      <c r="M34" s="42" t="n"/>
+      <c r="A34" s="42" t="inlineStr">
+        <is>
+          <t>TC-ALG-053</t>
+        </is>
+      </c>
+      <c r="B34" s="42" t="inlineStr">
+        <is>
+          <t>避障策略</t>
+        </is>
+      </c>
+      <c r="C34" s="42" t="inlineStr">
+        <is>
+          <t>相邻步下达的目标关节角不出现大幅跳变</t>
+        </is>
+      </c>
+      <c r="D34" s="42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E34" s="42" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F34" s="42" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="G34" s="42" t="inlineStr">
+        <is>
+          <t>策略每步重新解算目标角，跳变过大会使机械臂无法跟踪</t>
+        </is>
+      </c>
+      <c r="H34" s="42" t="inlineStr">
+        <is>
+          <t>目标 (0,0.85,0.2)，障碍 (0,0.6,0.2)，逐记录每步下达的 self.target</t>
+        </is>
+      </c>
+      <c r="I34" s="42" t="inlineStr">
+        <is>
+          <t>跑完整回合，计算相邻两步目标角之差的绝对值最大值</t>
+        </is>
+      </c>
+      <c r="J34" s="42" t="inlineStr">
+        <is>
+          <t>相邻步跳变 ≤ 30°</t>
+        </is>
+      </c>
+      <c r="K34" s="42" t="inlineStr">
+        <is>
+          <t>相邻步目标角最大跳变 177.4°（上限 30°），共 93 步</t>
+        </is>
+      </c>
+      <c r="L34" s="42" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="M34" s="42" t="inlineStr">
+        <is>
+          <t>场景法（策略可实施性）</t>
+        </is>
+      </c>
       <c r="N34" s="43" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="42" t="n"/>
-      <c r="B35" s="42" t="n"/>
-      <c r="C35" s="42" t="n"/>
-      <c r="D35" s="42" t="n"/>
-      <c r="E35" s="42" t="n"/>
-      <c r="F35" s="42" t="n"/>
-      <c r="G35" s="42" t="n"/>
-      <c r="H35" s="42" t="n"/>
-      <c r="I35" s="42" t="n"/>
-      <c r="J35" s="42" t="n"/>
-      <c r="K35" s="42" t="n"/>
-      <c r="L35" s="42" t="n"/>
-      <c r="M35" s="42" t="n"/>
+      <c r="A35" s="42" t="inlineStr">
+        <is>
+          <t>TC-ALG-054</t>
+        </is>
+      </c>
+      <c r="B35" s="42" t="inlineStr">
+        <is>
+          <t>端到端场景</t>
+        </is>
+      </c>
+      <c r="C35" s="42" t="inlineStr">
+        <is>
+          <t>抓取收敛后应留有余量而非贴着阈值</t>
+        </is>
+      </c>
+      <c r="D35" s="42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E35" s="42" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F35" s="42" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="G35" s="42" t="inlineStr">
+        <is>
+          <t>成功阈值为 0.05 m，最终距离应显著小于该阈值</t>
+        </is>
+      </c>
+      <c r="H35" s="42" t="inlineStr">
+        <is>
+          <t>目标 (0,0.85,0.2)，障碍 (0,0.6,0.2)</t>
+        </is>
+      </c>
+      <c r="I35" s="42" t="inlineStr">
+        <is>
+          <t>跑完整回合并记录最终夹爪-目标距离</t>
+        </is>
+      </c>
+      <c r="J35" s="42" t="inlineStr">
+        <is>
+          <t>最终距离 ≤ 0.04 m（预留 ≥20% 余量）</t>
+        </is>
+      </c>
+      <c r="K35" s="42" t="inlineStr">
+        <is>
+          <t>93 步结束，最终距离 0.04850 m（余量要求 ≤0.04，成功阈值 0.05），得分 100.00</t>
+        </is>
+      </c>
+      <c r="L35" s="42" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="M35" s="42" t="inlineStr">
+        <is>
+          <t>边界值分析（余量下界）</t>
+        </is>
+      </c>
       <c r="N35" s="43" t="n"/>
     </row>
     <row r="36">

--- a/附录1：测试用例清单（模块一）.xlsx
+++ b/附录1：测试用例清单（模块一）.xlsx
@@ -1411,7 +1411,7 @@
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="57" t="inlineStr">
         <is>
-          <t>2026.09.12</t>
+          <t>2026.09.13</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -1440,7 +1440,7 @@
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="57" t="inlineStr">
         <is>
-          <t>2026.09.12</t>
+          <t>2026.09.13</t>
         </is>
       </c>
       <c r="K10" s="11" t="n"/>
@@ -1469,7 +1469,7 @@
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="57" t="inlineStr">
         <is>
-          <t>2026.09.12</t>
+          <t>2026.09.13</t>
         </is>
       </c>
       <c r="K11" s="11" t="n"/>
@@ -1610,7 +1610,7 @@
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="60" t="inlineStr">
         <is>
-          <t>2026.09.12</t>
+          <t>2026.09.13</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="K2" s="42" t="inlineStr">
         <is>
-          <t>action=[100.0, 100.0, 100.0, 100.0, 29.4585, 0.0] shape=(6,)</t>
+          <t>action=[1.0, 1.0, 1.0, 1.0, 1.0, 0.0] shape=(6,)</t>
         </is>
       </c>
       <c r="L2" s="42" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="K21" s="42" t="inlineStr">
         <is>
-          <t>50 组样本动作最大绝对值 100.000（env 侧裁剪为 [-1,1]，单位：度/步）</t>
+          <t>50 组样本动作最大绝对值 1.000（env 侧裁剪为 [-1,1]，单位：度/步）</t>
         </is>
       </c>
       <c r="L21" s="42" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="K33" s="42" t="inlineStr">
         <is>
-          <t>最大动作绝对值 100.000（契约上限 1.0，env.py:122-123 据此裁剪）；最差样本 action=[100.0, 100.0, 100.0, 100.0, 29.458, 0.0]</t>
+          <t>最大动作绝对值 1.000（契约上限 1.0，env.py:122-123 据此裁剪）；最差样本 action=[1.0, 1.0, 1.0, 1.0, 1.0, 0.0]</t>
         </is>
       </c>
       <c r="L33" s="42" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M33" s="42" t="inlineStr">

--- a/附录1：测试用例清单（模块一）.xlsx
+++ b/附录1：测试用例清单（模块一）.xlsx
@@ -1411,7 +1411,7 @@
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="57" t="inlineStr">
         <is>
-          <t>2026.09.13</t>
+          <t>2026.09.14</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -1440,7 +1440,7 @@
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="57" t="inlineStr">
         <is>
-          <t>2026.09.13</t>
+          <t>2026.09.14</t>
         </is>
       </c>
       <c r="K10" s="11" t="n"/>
@@ -1469,7 +1469,7 @@
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="57" t="inlineStr">
         <is>
-          <t>2026.09.13</t>
+          <t>2026.09.14</t>
         </is>
       </c>
       <c r="K11" s="11" t="n"/>
@@ -1610,7 +1610,7 @@
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="60" t="inlineStr">
         <is>
-          <t>2026.09.13</t>
+          <t>2026.09.14</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="C20" s="42" t="inlineStr">
         <is>
-          <t>弃权返回 None 对下游调用的影响</t>
+          <t>动作返回值满足 (6,) 有限实数数组契约</t>
         </is>
       </c>
       <c r="D20" s="42" t="inlineStr">
@@ -3606,22 +3606,22 @@
       </c>
       <c r="H20" s="42" t="inlineStr">
         <is>
-          <t>起始关节角全 0、解算需超过 100° 变化的观测</t>
+          <t>起始关节角全 0、目标超出 ±100° 可达范围（旧版 D0 的弃权触发条件）</t>
         </is>
       </c>
       <c r="I20" s="42" t="inlineStr">
         <is>
-          <t>调用 get_action；对返回值执行 np.clip 模拟 env.step</t>
+          <t>调用 get_action；校验返回值的类型、形状与有限性</t>
         </is>
       </c>
       <c r="J20" s="42" t="inlineStr">
         <is>
-          <t>不返回 None，或调用方有明确处理，不导致运行中断</t>
+          <t>返回形状 (6,) 的有限实数数组；不返回 None、不含 NaN/Inf</t>
         </is>
       </c>
       <c r="K20" s="42" t="inlineStr">
         <is>
-          <t>未触发弃权路径，正常返回动作</t>
+          <t>返回形状 (6,) 的有限实数数组 action=[+1.000 -1.000 +1.000 -1.000 -1.000 +0.000]</t>
         </is>
       </c>
       <c r="L20" s="42" t="inlineStr">

--- a/附录1：测试用例清单（模块一）.xlsx
+++ b/附录1：测试用例清单（模块一）.xlsx
@@ -3596,7 +3596,7 @@
       </c>
       <c r="F20" s="42" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>修改</t>
         </is>
       </c>
       <c r="G20" s="42" t="inlineStr">

--- a/附录1：测试用例清单（模块一）.xlsx
+++ b/附录1：测试用例清单（模块一）.xlsx
@@ -1411,7 +1411,7 @@
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="57" t="inlineStr">
         <is>
-          <t>2026.09.14</t>
+          <t>2026.09.22</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -1440,7 +1440,7 @@
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="57" t="inlineStr">
         <is>
-          <t>2026.09.14</t>
+          <t>2026.09.22</t>
         </is>
       </c>
       <c r="K10" s="11" t="n"/>
@@ -1469,7 +1469,7 @@
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="57" t="inlineStr">
         <is>
-          <t>2026.09.14</t>
+          <t>2026.09.22</t>
         </is>
       </c>
       <c r="K11" s="11" t="n"/>
@@ -1610,7 +1610,7 @@
     <row r="20" ht="16.2" customHeight="1">
       <c r="B20" s="60" t="inlineStr">
         <is>
-          <t>2026.09.14</t>
+          <t>2026.09.22</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
